--- a/www/download/COUNTRY.AUT.EXI382.xlsx
+++ b/www/download/COUNTRY.AUT.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Áustria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.308</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.836</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.316</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.099</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.552</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.649</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.69</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.525</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3.581</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3.605</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.828</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.874</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>3.941</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.919</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.073</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.111</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.203</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.187</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.226</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.336</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.494</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4.672</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>4.898</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.899</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4.896</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.174</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.873</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.659</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.041</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.145</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.175</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.031</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.081</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.095</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.292</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.329</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.385</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.375</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.491</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.497</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.527</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.592</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.617</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.609</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.642</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.741</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.878</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>4.021</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>4.236</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4.231</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7606.846</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5908.125</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5639.058</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>6498.084</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6575.463</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6672.371</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6380.48</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6433.899</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6774.349</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6431.561</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6840.452</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6833.372</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6882.429</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6800.796</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7019.697</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6813.569</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6845.039</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6981.695</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6930.619</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>6851.132</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>6876.885</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7014.481</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>7210.408</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7457.122</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>7756.704</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>7727.874</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>7728.427</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6423.358</t>
+          <t>10067302644.2584</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3495.349</t>
+          <t>8990556206.09732</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3125.707</t>
+          <t>8742849599.65601</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5126.097</t>
+          <t>9204051123.12158</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3873.885</t>
+          <t>9949392766.04356</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4549.782</t>
+          <t>10027988367.55</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5026.09</t>
+          <t>10761969455.0045</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5089.078</t>
+          <t>9975375574.75127</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>10091546016.502</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5071.931</t>
+          <t>10560913858.196</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5422.011</t>
+          <t>10762555576.3864</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5448.219</t>
+          <t>10779779300.0264</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5489.267</t>
+          <t>10379870501.2109</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5459.136</t>
+          <t>11219669573.0171</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5666.383</t>
+          <t>10449426885.9135</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>10926637995.4288</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5549.864</t>
+          <t>11914539840.4298</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>12219069812.6929</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5646.745</t>
+          <t>11936226128.6729</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5613.976</t>
+          <t>10402760827.0911</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5658.687</t>
+          <t>10091779852.4722</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5802.243</t>
+          <t>10114301326.7636</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5994.702</t>
+          <t>9930809575.44356</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6191.6</t>
+          <t>11057067024.3782</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>6482.903</t>
+          <t>11361966926.928</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>6487.264</t>
+          <t>11945878743.3438</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6503.053</t>
+          <t>12048887635.2972</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5685727197.10292</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4449490662.53845</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4741161052.9765</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4989427601.86334</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5365901664.97403</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4940994797.0098</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5162015298.16883</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4848747417.2342</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4935386013.15534</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4769958560.06604</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4720571447.6805</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4847936500.74692</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4185986359.80727</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4502914644.58803</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4895554291.70103</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5041129080.30852</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5137334672.66185</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4932022938.8693</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4957088842.5258</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4624569792.02901</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4514884496.41789</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5764657385.07529</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>5535973998.76722</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6404258147.18354</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>5851513988.1227</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6539179421.47448</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5410329763.14793</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6766343.92269162</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6121786.35239903</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5819065.18337622</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6014393.14206309</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6077950.02417771</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5647185.322014</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5934896.85470918</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5466533.21584615</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5362317.20646748</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5324948.13458416</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5001207.46765156</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4421966.53071547</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4138275.54758323</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4042374.40626261</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4168860.67183021</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4035273.2013378</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3850808.96318453</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4111525.12813902</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4109764.53428274</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3375676.09016478</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2921267.66612004</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2852772.76152629</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2522507.45830726</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2731074.96067939</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2762671.55537505</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2790709.17854698</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2881219.61528227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15045.2527953491</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>27659.3166033848</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>30456.7431723926</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31462.8900602236</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>32948.1996779712</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>39614.0087022591</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>39757.7119373542</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>38169.1111754865</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>34609.4032547455</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>34010.4772440022</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>36691.8373536054</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>39229.9126387772</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>40358.9931889688</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>41000.0727752865</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>41589.3617184725</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>46056.1725541048</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>47986.1303661452</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>54158.5755441038</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>52401.5770700159</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>53119.1704019847</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>59935.7170573554</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>55314.7009057134</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>61928.4487133102</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>62265.1364080081</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>68586.282349441</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>65559.1335563581</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>64716.8355073611</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>37526.9039298849</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>68319.8877927701</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>72361.2789897087</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>78316.728159814</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>89298.733618848</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>107588.416669781</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>115936.022396127</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>104169.223169573</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>96805.9964507622</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>99002.460978579</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>108161.227275595</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>115885.968143972</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>115610.085763681</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>125565.038935017</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>117191.880557511</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>141318.139899647</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>160421.067084372</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>181591.862354826</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>173277.947019303</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>156314.368762066</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>171299.356109284</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>156482.783568427</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>162439.152442838</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>175900.849829074</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>192583.870722272</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>192620.808354711</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>190741.845474591</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.129733780839015</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.214438400910031</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.34072963034264</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.0273917990283663</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.278055163535807</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0791768748056187</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.0263318278462337</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0495654984853187</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0877777312031252</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0633071411696511</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.14859208468568</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.123822269363254</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.3113437379317</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.212356091750763</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.15745483807714</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0904824916047213</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0803002633900842</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.145839155666015</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.139125236480751</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.213945531594634</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.253340283714377</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.00651998099293594</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.0828631420682726</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.0332057462535601</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.10790187857069</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.00793914846655197</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.201969746598689</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1362.24578365128</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1548.4837608238</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1783.07510886773</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1640.6168644062</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1706.38065291826</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1556.11100868839</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1703.15762844376</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1573.71681917815</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1514.1078700312</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1541.06756527502</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1434.131057538</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1456.16037820626</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1236.45283971801</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1334.24041808389</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1402.35990641542</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1441.7313718858</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1456.54457457946</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1373.22964705214</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1370.64511864052</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1281.54902000812</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1239.64783521072</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1540.75945975214</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1427.39089967301</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1592.73233737704</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1383.22758485653</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1543.60848542135</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1278.68108397394</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>5386196280.95787</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>4738925176.67823</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>4579329404.39875</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>4870108798.0843</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>5795416188.53562</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>6139121827.83479</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>6766280744.73163</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>7100176489.0153</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>7013697328.3926</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>7671484691.00818</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>7484763792.87723</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>7597429434.08005</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>7063340765.7437</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>8026672788.10025</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>7309911722.85209</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>7689340789.19515</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>7536178088.36793</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>7702595143.05582</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>7593335808.94039</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>7347478618.29375</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>7336827518.53081</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>8330419731.79087</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>7121890095.75646</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>8129158689.27125</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>7875467726.75488</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>8667069519.32609</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>8201718561.56791</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3179115780.15907</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3873514194.1492</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3581026780.03167</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3715297129.57691</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4616222248.82317</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4934606127.3235</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5357417083.14117</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5336565243.21482</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5363929441.56947</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6357312024.05435</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5989192394.23677</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6134731483.13059</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>5666092017.70816</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6325269990.43352</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5779315821.61965</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>6150698715.54639</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6095625830.80631</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>6180998644.57535</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6182100019.90774</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>5897754733.04819</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>5841691467.98731</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>6693107340.72588</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>5838811834.00369</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>6860554092.72206</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>6686647562.71725</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>7426179495.88772</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>8169355868.39005</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2207080500.7988</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>865410982.529034</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>998302624.367086</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1154811668.50738</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1179193939.71245</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1204515700.5113</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1408863661.59046</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1763611245.80049</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1649767886.82314</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1314172666.95383</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1495571398.64045</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1462697950.94947</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1397248748.03553</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1701402797.66673</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1530595901.23244</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1538642073.64876</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1440552257.56162</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1521596498.48047</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1411235789.03265</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1449723885.24557</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1495136050.5435</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1637312391.065</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1283078261.75277</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1268604596.54919</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1188820164.03763</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1240890023.43837</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>32362693.1778647</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>1538.97507959637</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>1216.42937931759</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>1175.52858615006</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>1685.55631183856</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1231.91270141674</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>1432.90300216982</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>1658.31037497658</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>1651.71887779544</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1647.01282365934</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1638.62814718186</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>1647.23158109006</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>1636.46546079261</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>1621.41468861208</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>1617.57449872408</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1623.16825840593</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>1572.18281863872</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>1573.50548755759</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>1573.50029931377</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>1561.33644490257</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>1555.73070635834</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>1553.70056948891</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>1550.80518214441</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>1545.66899457957</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1539.84447153226</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>1532.48043975335</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>1531.35354848136</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>1536.93597848469</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1572.86981997554</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1781.67548740229</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1819.59097538673</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1829.38978899512</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1802.10893563865</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1808.34333847329</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>1809.81880481464</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1796.64652365459</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>1792.18426747504</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>1784.28462835988</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1786.7978988229</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>1763.98800150732</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1746.17562661339</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1735.17580631556</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1728.90849935588</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1673.0185973637</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>1665.22056444444</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>1670.43779728026</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1648.97346888748</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1636.40942018462</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1627.41214155982</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>1617.69089937784</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>1604.39194296121</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1596.18083534575</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1583.56936967511</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>1577.5934376818</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1578.43878770563</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>54671.2477935392</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>60811.4727556308</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>68436.9168405506</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>73340.417510283</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>80456.5175477532</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>95770.2973512238</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>103400.556893697</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>107457.990541896</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>102434.141317581</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>107929.050406966</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>117597.867328311</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>128741.79286931</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>137942.453118198</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>140256.075322619</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>119657.195139859</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>142802.253410164</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>152815.90824277</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>163537.458326148</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>162545.895783458</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>169267.123085669</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>181913.694296124</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>186410.978580167</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>197522.068573234</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>213903.263078236</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>222423.444515649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>226176.39886861</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>230899.046171859</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1773832166.72544</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1740798053.49397</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1760857118.97766</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1983924659.80045</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2293150667.30916</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2555415579.83295</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2780734669.7815</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2841320420.83114</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2683829924.37769</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2928179436.30748</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3005823065.5054</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3059133598.11789</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2913050140.92524</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3155350406.11621</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2593601935.72165</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3074650420.24329</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3370190596.25616</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3423599565.34747</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3379241775.17491</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2949384480.83225</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2837267169.35327</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2745914767.61965</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2871151512.67421</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3491686561.44019</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>3617184033.11813</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3840176649.34684</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3827045828.19359</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>57537.6713299467</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>64692.5887923227</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>70433.3776245893</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>73915.1379843457</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>79247.1990069808</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>92070.5533877975</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>98502.9459508202</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96533.0309534212</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>94121.327451661</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>98596.858556351</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>106968.555555661</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>116118.563079034</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>121619.989478631</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>123324.285468313</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>107113.513522384</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>129266.105593876</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>141518.924556345</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>151897.456972681</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>150631.82134657</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>155038.584794275</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>165030.399952223</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>168504.903446296</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>182239.844182029</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>197427.095357868</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>204889.685873792</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>207934.324981902</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>212390.538270462</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7606.846</t>
+          <t>8783932595.14724</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5908.125</t>
+          <t>7268125569.09781</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5639.058</t>
+          <t>6713899459.99325</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6498.084</t>
+          <t>6962309829.97036</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6575.463</t>
+          <t>7866724755.02221</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6672.371</t>
+          <t>8120556989.32026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6380.48</t>
+          <t>8757133675.29475</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6433.899</t>
+          <t>8113384630.12796</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6774.349</t>
+          <t>8285365909.37351</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6431.561</t>
+          <t>8888234941.5869</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6840.452</t>
+          <t>8712828253.52231</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6833.372</t>
+          <t>8778331217.33587</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6882.429</t>
+          <t>7949428132.41031</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6800.796</t>
+          <t>8861701727.60649</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7019.697</t>
+          <t>8057191474.90267</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6813.569</t>
+          <t>9094956889.60815</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6845.039</t>
+          <t>9603648478.13335</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6981.695</t>
+          <t>9857071025.64985</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6930.619</t>
+          <t>9607777981.2937</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>6851.132</t>
+          <t>8784282790.79001</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>6876.885</t>
+          <t>8542073008.68561</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>7014.481</t>
+          <t>9177278273.61817</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>7210.408</t>
+          <t>8521015621.62468</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7457.122</t>
+          <t>9983283782.42515</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>7756.704</t>
+          <t>9892391089.48984</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7727.874</t>
+          <t>10737011121.9244</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7728.427</t>
+          <t>10225386553.0198</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6423.358</t>
+          <t>-2866.42353640754</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3495.349</t>
+          <t>-3881.11603669196</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3125.707</t>
+          <t>-1996.46078403875</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5126.097</t>
+          <t>-574.720474062715</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3873.885</t>
+          <t>1209.31854077244</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4549.782</t>
+          <t>3699.74396342633</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5026.09</t>
+          <t>4897.61094287639</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5089.078</t>
+          <t>10924.9595884745</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>8312.81386591967</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5071.931</t>
+          <t>9332.1918506151</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5422.011</t>
+          <t>10629.3117726502</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5448.219</t>
+          <t>12623.2297902764</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5489.267</t>
+          <t>16322.4636395667</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5459.136</t>
+          <t>16931.7898543054</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5666.383</t>
+          <t>12543.6816174755</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>13536.1478162875</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5549.864</t>
+          <t>11296.9836864251</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>11640.0013534672</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5646.745</t>
+          <t>11914.0744368878</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5613.976</t>
+          <t>14228.5382913939</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>5658.687</t>
+          <t>16883.2943439006</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>5802.243</t>
+          <t>17906.0751338706</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>5994.702</t>
+          <t>15282.2243912053</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6191.6</t>
+          <t>16476.1677203687</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>6482.903</t>
+          <t>17533.7586418565</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>6487.264</t>
+          <t>18242.0738867083</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>6503.053</t>
+          <t>18508.5079013976</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8762.459</t>
+          <t>-7010100428.4218</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8075.973</t>
+          <t>-5527327515.60385</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7939.189</t>
+          <t>-4953042341.01559</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8306.067</t>
+          <t>-4978385170.16991</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8900.748</t>
+          <t>-5573574087.71305</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8930.906</t>
+          <t>-5565141409.48731</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9437.546</t>
+          <t>-5976399005.51324</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8855.672</t>
+          <t>-5272064209.29682</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8987.029</t>
+          <t>-5601535984.99582</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9323.437</t>
+          <t>-5960055505.27942</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9463.634</t>
+          <t>-5707005188.01692</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9447.793</t>
+          <t>-5719197619.21798</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9143.598</t>
+          <t>-5036377991.48507</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9891.437</t>
+          <t>-5706351321.49028</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9313.096</t>
+          <t>-5463589539.18102</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9596.454</t>
+          <t>-6020306469.36486</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10341.768</t>
+          <t>-6233457881.87718</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10679.946</t>
+          <t>-6433471460.30238</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>10423.451</t>
+          <t>-6228536206.11879</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>9125.13</t>
+          <t>-5834898309.95776</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>8891.891</t>
+          <t>-5704805839.33233</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>-6431363505.99851</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>8834.985</t>
+          <t>-5649864108.95047</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>9704.933</t>
+          <t>-6491597220.98496</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>10008.647</t>
+          <t>-6275207056.37171</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10451.357</t>
+          <t>-6896834472.57758</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>10546.883</t>
+          <t>-6398340724.82621</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>87355.0628038371</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>92040.2056441552</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>91840.5015238332</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>94664.2117575304</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>96472.3956044669</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>100289.183168839</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>103930.313230888</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>104668.930215154</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>108498.705134353</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>105754.025117137</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>111346.768998887</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>118318.269094652</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>122160.622417453</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>126703.781311444</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>128470.548029033</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>131645.220327681</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>136536.232128208</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>139081.656900771</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>141054.11748725</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>143135.122614978</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>146534.146280508</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>157246.78728052</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>163618.359735763</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>175758.547933803</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>179578.902226305</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>180070.500645601</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>179727.118542648</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4036.174</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3639.828</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3679.851</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3697.627</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3670.988</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3692.301</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3690.581</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3655.122</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3607.859</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>3628.008</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3651.012</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3649.189</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>3623.569</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3663.498</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>3708.32</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>3561.037</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>3563.95</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>3644.257</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>3609.675</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3535.094</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3531</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3575.279</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>3786.031</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3913.965</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>4046.419</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>4065.82</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4088.069</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>126317.228016736</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>124751.628965015</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>135498.165200572</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>142219.15348384</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>149158.440885337</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>145445.606079907</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>153240.637505541</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>160737.984917007</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>161822.076886734</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>164818.750446744</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>177798.678438721</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>186683.374528114</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>189260.600007733</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>192644.57267525</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>204011.98934295</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>210316.615546683</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>218576.826698087</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>211825.778896267</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>221555.552742093</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>224813.801965894</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>231135.833575785</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>254596.000438183</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>259993.147232401</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>284978.487946371</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>284078.972998634</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>289053.113290093</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>284289.42787834</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4809.668</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3750.433</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>4033.841</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4209.051</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>4502.84</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4143.609</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4293.354</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4066.706</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4150.354</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4043.466</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>3981.681</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>4090.241</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3539.566</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3809.934</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4152.836</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>4231.61</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>4284.661</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>4116.434</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>4129.686</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>3895.95</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3791.597</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>4862.151</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>4684.657</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>5409.103</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>4975.931</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>5510.589</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4541.089</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>33.55</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-6.8</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-22.51</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-13.97</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>25.14</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>36.17</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>55.08</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>36.45</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>29.91</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>29.53</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>37.29</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>36.74</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17.72</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>43.2</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7.624</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.24</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.937</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.139</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>7.134</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.635</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.885</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6.36</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.271</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.233</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5.829</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>5.158</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.868</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.73</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>4.664</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>4.377</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4.729</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>4.716</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3.875</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>3.395</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3.307</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.949</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>3.167</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>3.211</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>3.223</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>3.323</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>103278.34227297</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>105746.12619049</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>96030.5630300195</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>99810.7494722188</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>103088.893511748</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>118717.279516541</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>118811.967450925</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>118544.006836102</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>124425.937534331</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>133748.745700637</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>135358.867568976</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>143435.345196259</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>162382.33687926</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>169791.909298608</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>148788.721799651</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>153846.583970316</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>162538.663103132</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>180251.516226512</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>177468.012509822</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>184363.844091985</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>192268.928241195</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>186840.988785284</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>193347.01985506</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>185509.024120079</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>203222.892669507</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>208524.588659266</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>219007.004234002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6423358083.2023</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3495348999.99959</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3125707000.00089</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5126097000.00016</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3873885000.00261</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4549782270.55174</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5026089999.99783</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5089077999.99881</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5368603000.00175</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5071931000.00152</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5422010999.99905</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5448218999.99835</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5489267000.00078</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5459136000.00002</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5666382999.99866</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5497262999.99586</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5549863999.99961</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5651304999.99942</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5646744999.99829</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5613975834.58114</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>5658686615.67804</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5802242841.65677</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5994702198.71333</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>6191599976.20587</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>6482903339.92381</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>6487263905.19797</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>6503052694.42626</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7606845527.58681</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5908124999.99959</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5639058000.0008</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6498084000.00022</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6575463000.00189</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6672371000.00139</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6380479999.99792</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6433898999.99918</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6774349000.00146</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6431561000.00082</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6840451999.99942</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6833371999.99887</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6882429000.00111</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6800796000.00004</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7019696999.9988</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6813568999.99573</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6845038999.99959</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6981694999.99962</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6930618999.99826</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>6851132147.63429</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>6876885400.09145</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>7014480697.08822</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>7210408331.24225</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7457121568.03781</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>7756704192.413</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>7727874279.24316</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7728427196.12385</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4036173981.55603</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3639827999.99984</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3679851000.00028</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3697627000.00081</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3670988000.00199</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3692301000.00027</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3690580999.99962</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3655121999.99902</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3607859000.00089</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3628008000.0007</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3651011999.99985</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3649189000.00001</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3623569000.00116</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3663498000.00009</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3708319999.99964</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3561036999.99919</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3563950000.00091</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3644256999.99886</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3609674999.99933</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3535094242.46509</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3531000206.77844</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3575278634.50578</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3786030782.76294</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3913965095.75933</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>4046419197.89377</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>4065819610.41689</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4088069281.28458</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4836284.24360325</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3316049.99999957</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3099079.99999961</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3552050.00000005</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3648760.00000057</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3689770.00000155</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3525480</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3581060.00000038</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3779940.00000104</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3604559.99999996</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3828329.99999929</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3873819.99999988</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3941429.99999902</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3919370.00000059</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4060189.99999946</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4072620.00000022</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4110589.99999996</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4179559.99999935</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4202989.99999931</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4186685.83981957</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4225656.93377473</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4336106.9162137</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4494168.87368187</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>4671852.58894711</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>4898240.86077417</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4898520.8068556</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4896247.64439402</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4173789.53588187</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2873449.99999955</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2658979.99999966</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3041189.99999991</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3144610.00000043</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3175220.00000145</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3030850.00000004</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3081080.0000005</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3259600.00000108</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3095229.99999989</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3291589.99999929</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3329259.99999996</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3385479.99999899</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3374890.00000068</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3490939.99999942</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3496580.00000006</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3527069.99999991</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3591549.9999994</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3616609.99999948</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3608578.15021365</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3642070.24622476</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3741438.90442356</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3878386.78251025</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>4020925.54843851</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>4230333.49839507</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>4236294.0364956</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4231179.94858693</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7606845527.58681</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5908124999.99959</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5639058000.0008</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6498084000.00022</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6575463000.00189</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6672371000.00139</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6380479999.99792</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6433898999.99918</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6774349000.00146</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6431561000.00082</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6840451999.99942</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6833371999.99887</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6882429000.00111</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6800796000.00004</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7019696999.9988</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6813568999.99573</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6845038999.99959</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6981694999.99962</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6930618999.99826</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>6851132147.63429</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>6876885400.09145</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>7014480697.08822</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>7210408331.24225</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>7457121568.03781</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>7756704192.413</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>7727874279.24316</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>7728427196.12385</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6423358083.2023</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3495348999.99959</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3125707000.00089</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5126097000.00016</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3873885000.00261</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4549782270.55174</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5026089999.99783</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5089077999.99881</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5368603000.00175</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5071931000.00152</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5422010999.99905</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5448218999.99835</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5489267000.00078</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5459136000.00002</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5666382999.99866</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5497262999.99586</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5549863999.99961</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5651304999.99942</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5646744999.99829</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5613975834.58114</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>5658686615.67804</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>5802242841.65677</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>5994702198.71333</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>6191599976.20587</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>6482903339.92381</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>6487263905.19797</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>6503052694.42626</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>391020.908102254</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>403700.145406576</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>408747.379142458</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>429187.186702247</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>448819.814674426</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>477517.781937716</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>505401.949213838</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>519300.641096725</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>540595.744103906</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>562753.847825713</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>603593.701192323</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>648275.277486624</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>687956.488101835</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>723748.651390222</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>683703.678855762</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>726052.591077183</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>772965.798284599</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>797176.098793183</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>808311.024420961</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>828402.032472174</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>860314.821061565</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>887079.352557232</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>931975.633503074</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>980520.984029278</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1010749.93740505</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1028216.33809791</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1043811.73098384</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>137776.102702318</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>138675.65576445</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>149405.448353334</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>154829.386734769</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>163443.997005056</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>159989.859012893</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169392.18197627</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>176623.950797295</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>178159.705298358</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>182675.26448117</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>196836.502666927</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>206567.522234995</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>208564.263984617</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>212888.113132108</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>226457.791721526</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>232813.831267302</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>242565.766204408</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>236566.826142086</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>246091.867444322</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>250811.873116411</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>257859.396399497</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>280593.997932669</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>289743.29863971</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>318524.912685814</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>316793.732902749</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>320332.319547597</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>318047.186050308</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
